--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">重标定时 exp 与 exp2 怎样匹配？</t>
+          <t xml:space="preserve">在 Attention 在线 softmax 的手算中，score 已乘原始 sm_scale，但尚未除以 ln2，也没有取 exp 或 exp2。旧、新运行最大分数分别为 −15 和 −13，而 kernel 使用 exp2。旧状态应乘什么重标定系数？为什么不能直接写 2^(−2)？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09-24 A4：已乘原始 scale、尚未取指数，旧／新 score 为 −15／−13。</t>
+          <t xml:space="preserve">A4 变式使用自然指数形式 softmax 的分数；要把已经积累的分母和加权 V 分子换到新的最大值基准。此前题目“自然指数 score”的措辞曾使表示域不够明确。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha=e^(−2)=2^(−2/ln2)；先确认 score 的表示域。</t>
+          <t xml:space="preserve">系数为 exp(−15−(−13))=e^(−2)。使用 exp2 时必须先把分数差除以 ln2，即 2^(−2/ln2)。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,27 +61,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：自然指数分数 s 必须先换成 x=s/ln2，才能直接送入 exp2。
-[E##x=s/\ln2,\quad e^s=2^x,\quad \alpha=2^{x_{old}-x_{new}}=e^{s_{old}-s_{new}}]
-• [T#B#修正范围]：旧 l 和 acc 都要乘同一个 alpha，这个判断原本正确；错误仅在指数底数与 score 标度不匹配。
-[T#B,!c47f17#边界]：先前题目“自然指数 score”措辞造成了歧义；换成 score 从 1 到 4 后，你已独立答对 e⁻³。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：exp2 的输入与自然指数 exp 的输入不是同一标度；先确定 score 是否已完成换底，再计算系数。
+• [T#B#定义]：令 s_j 表示已乘原始 sm_scale 的点积分数，x_j=s_j/ln2 表示供 exp2 使用的分数。两者均尚未取指数。
+[E##e^{s_j}=2^{x_j},\quad x_j=s_j/\ln2,\qquad \alpha=2^{x_{old}-x_{new}}=e^{s_{old}-s_{new}}]
+• [T#B#代入]：这里自然分数差为 −2，因此 alpha=e⁻²。把 −2 直接交给 exp2 相当于跳过换底，得到的 1/4 不是相同权重基准。
+• [T#B#用于状态]：旧分母 l 与旧加权 V 分子 acc 都乘同一个 alpha。原答关于二者都需要重标定的判断正确，需要修正的是这个系数。
+[T#B,!c47f17#边界]：题目必须注明给出的分数处于哪个表示域。后来把自然分数改为从 1 到 4，你独立得到 e⁻³，说明已区分原始 sm_scale 与 kernel 内融合换底后的缩放。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前向保存量、反向临时量和梯度如何区分？</t>
+          <t xml:space="preserve">在所学 PyTorch/Triton Attention 的前后向流程中，哪些量是在前向结束时保存给反向使用的，哪些是在反向中临时计算的，哪些才是最终输出的梯度？请按产生时间和用途区分。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09-19：所学官方 attention 的前后向数据流</t>
+          <t xml:space="preserve">前向已用 Q/K/V 计算 O，随后损失函数会提供上游梯度 dO。需要梳理自动求导上下文保存的输入，与反向运算新产生的中间量和输出。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">前向保存 Q/K/V/O/M；反向临时生成 Delta、重算 P；最终返回 dQ/dK/dV。</t>
+          <t xml:space="preserve">前向保存 Q/K/V/O/M；反向用 O、dO 生成 Delta 并按块重建 score/P；最终输出 dQ/dK/dV。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -91,27 +93,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：按量的产生时间和用途区分；最终梯度不能当成前向已保存输入。
-• [T#B#前向]：Q/K/V/O/M 交给自动求导上下文，用于后续反向。
-• [T#B#反向]：先用 O、dO 求 Delta；主 kernel 按块重建 score/P，计算三个输入梯度。
-[T#B,!c47f17#边界]：这是所学官方实现的保存策略，不能推广为所有 Attention 实现都保存相同量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前向保存量是反向开始前已有的依据；Delta 和概率块是反向过程中的计算材料；dQ/dK/dV 则要到反向完成后才产生。
+• [T#B#前向保存]：Q/K/V 是原输入，O 是前向输出，M 是每个 query 的 base-2 log-sum-exp。官方 wrapper 把这些量交给 ctx，以便之后求输入梯度。
+• [T#B#反向临时量]：损失传来 dO 后，预处理先计算逐 query 的 Delta=sum_d(O*dO)。主反向利用 Q/K 和 M 按 tile 恢复概率 P，而非读取一张前向保存的完整 P。
+• [T#B#最终梯度]：dQ、dK、dV 分别描述损失对三个输入张量的导数。它们是反向的结果，不能列为前向就已保存的数据。
+[T#B,!c47f17#边界]：这是本课官方实现的保存策略。其他 Attention 实现可能选择不同的保存/重算取舍；分类时仍按每个量何时产生、由谁消费来判断。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delta 应沿哪个维度归约？</t>
+          <t xml:space="preserve">Attention 反向预处理拿到前向输出 O 和上游梯度 dO，两者都是 \[B,H,N,D\]：N 是 query 数，D 是每个输出向量的特征数。为了得到每个 query 一个 Delta，实际应沿哪一维求和？它与沿 key 求和的公式有什么关系？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">09-19：反向预处理归约轴表述</t>
+          <t xml:space="preserve">要为 softmax 反向准备逐 query 的标量统计量。这里 i 标识 query，j 标识 key，d 标识输出特征，三个索引代表不同的归约方向。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">沿特征 D 求和；每个 query 留一个值。</t>
+          <t xml:space="preserve">实际预处理沿特征 d 求和：Delta_i=Σ_d O_id*dO_id，结果为 \[B,H,N\]。它等于 Σ_j P_ij*dP_ij，但两式的归约轴不同。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -121,9 +124,13 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：O 与 dO 每行都是 D 维向量，它们的行内点积得到 Delta。
-[E##\Delta_i=\sum_dO_{id}\,dO_{id}=\sum_jP_{ij}\,dP_{ij}]
-• [T#B#区分]：实际预处理归约的是特征 d；右边对 key j 的和是等价恒等式，不能混淆实现归约轴。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：对同一个 query，O\[i,:\] 和 dO\[i,:\] 都是 D 维向量；做这两个向量的点积，才得到该 query 的 Delta。
+• [T#B#概率与梯度]：P_ij 是 query i 对 key j 的 softmax 概率，dP_ij 是损失对该概率的梯度；它们都用 query×key 两个轴索引。
+[E##\Delta_i=\sum_d O_{id}\,dO_{id}=\sum_j P_{ij}\,dP_{ij}]
+• [T#B#恒等式来源]：由 O_id=Σ_j P_ij V_jd 和 dP_ij=Σ_d dO_id V_jd，交换有限求和顺序，就得到两个表达式相等。
+• [T#B#实现意义]：右边需要该 query 对所有 key 的 P/dP；左边只需已经保存的 O 和传入的 dO，所以预处理不必为计算 Delta 再物化整行概率。
+• [T#B#反向用途]：之后每个 query 的 Delta 可以在扫描多个 key 块时复用，用在 dS_ij=P_ij(dP_ij−Delta_i) 中。
+[T#B,!c47f17#边界]：实际代码中的 O*dO 归约轴是特征 D。不能因为等价式右边对 key j 求和，就把左边也说成“对 j 求和”。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Attention 在线 softmax 的手算中，score 已乘原始 sm_scale，但尚未除以 ln2，也没有取 exp 或 exp2。旧、新运行最大分数分别为 −15 和 −13，而 kernel 使用 exp2。旧状态应乘什么重标定系数？为什么不能直接写 2^(−2)？</t>
+          <t xml:space="preserve">在线 softmax 手算：score 已乘原始 sm_scale，属于自然指数域（softmax 权重为 e^score），还没有取指数。旧、新运行最大分数分别为 −15 和 −13。旧分母和旧分子都要乘同一个重标定系数，它等于多少？请分别写出用 exp 和用 exp2 表示的形式。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4 变式使用自然指数形式 softmax 的分数；要把已经积累的分母和加权 V 分子换到新的最大值基准。此前题目“自然指数 score”的措辞曾使表示域不够明确。</t>
+          <t xml:space="preserve">要把已累积的分母 l 和加权 V 分子 acc 换到新最大值的基准上；kernel 内部用 exp2 计算指数。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">系数为 exp(−15−(−13))=e^(−2)。使用 exp2 时必须先把分数差除以 ln2，即 2^(−2/ln2)。</t>
+          <t xml:space="preserve">系数为 e^(−15−(−13))=e^(−2)；改用 exp2 时要先把自然分数差除以 ln2，写成 2^(−2/ln2)，数值仍是 e^(−2)。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,19 +61,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：exp2 的输入与自然指数 exp 的输入不是同一标度；先确定 score 是否已完成换底，再计算系数。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把自然指数域的分数差 −2 直接交给 exp2，跳过了换底；判断旧分母和旧分子都要重标定是对的。
 • [T#B#定义]：令 s_j 表示已乘原始 sm_scale 的点积分数，x_j=s_j/ln2 表示供 exp2 使用的分数。两者均尚未取指数。
 [E##e^{s_j}=2^{x_j},\quad x_j=s_j/\ln2,\qquad \alpha=2^{x_{old}-x_{new}}=e^{s_{old}-s_{new}}]
 • [T#B#代入]：这里自然分数差为 −2，因此 alpha=e⁻²。把 −2 直接交给 exp2 相当于跳过换底，得到的 1/4 不是相同权重基准。
-• [T#B#用于状态]：旧分母 l 与旧加权 V 分子 acc 都乘同一个 alpha。原答关于二者都需要重标定的判断正确，需要修正的是这个系数。
-[T#B,!c47f17#边界]：题目必须注明给出的分数处于哪个表示域。后来把自然分数改为从 1 到 4，你独立得到 e⁻³，说明已区分原始 sm_scale 与 kernel 内融合换底后的缩放。</t>
+• [T#B#用于状态]：旧分母 l 与旧加权 V 分子 acc 都乘同一个 alpha；原答在这一点上正确，需要修正的只是系数。
+[T#B,!c47f17#边界]：给定分数时先确认它处于哪个表示域：只有已换到 exp2 输入域、已含 1/ln2 的分数差，才能直接作为 2 的指数。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">在所学 PyTorch/Triton Attention 的前后向流程中，哪些量是在前向结束时保存给反向使用的，哪些是在反向中临时计算的，哪些才是最终输出的梯度？请按产生时间和用途区分。</t>
+          <t xml:space="preserve">在 Triton 官方 fused-attention 教程（快照版）的前后向流程中，哪些量是在前向结束时保存给反向使用的，哪些是在反向中临时计算的，哪些才是最终输出的梯度？请按产生时间和用途区分。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -93,11 +93,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前向保存量是反向开始前已有的依据；Delta 和概率块是反向过程中的计算材料；dQ/dK/dV 则要到反向完成后才产生。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把反向的最终输出 dQ/dK/dV 当成保存量；原答“重新计算了 P”是对的，只是没有说出前向真正保存的 Q/K/V/O/M。
 • [T#B#前向保存]：Q/K/V 是原输入，O 是前向输出，M 是每个 query 的 base-2 log-sum-exp。官方 wrapper 把这些量交给 ctx，以便之后求输入梯度。
 • [T#B#反向临时量]：损失传来 dO 后，预处理先计算逐 query 的 Delta=sum_d(O*dO)。主反向利用 Q/K 和 M 按 tile 恢复概率 P，而非读取一张前向保存的完整 P。
 • [T#B#最终梯度]：dQ、dK、dV 分别描述损失对三个输入张量的导数。它们是反向的结果，不能列为前向就已保存的数据。
-[T#B,!c47f17#边界]：这是本课官方实现的保存策略。其他 Attention 实现可能选择不同的保存/重算取舍；分类时仍按每个量何时产生、由谁消费来判断。</t>
+[T#B,!c47f17#边界]：这是该教程的保存策略。其他 Attention 实现可能选择不同的保存与重算取舍；分类时仍按每个量何时产生、由谁消费来判断。</t>
         </is>
       </c>
     </row>
@@ -124,7 +124,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：对同一个 query，O\[i,:\] 和 dO\[i,:\] 都是 D 维向量；做这两个向量的点积，才得到该 query 的 Delta。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原答“O 与 dO 相乘”是对的，错在归约轴：实现对同一 query 的 D 个特征求和，即 O\[i,:\] 与 dO\[i,:\] 两个 D 维向量的点积，而不是对 key j 求和。
 • [T#B#概率与梯度]：P_ij 是 query i 对 key j 的 softmax 概率，dP_ij 是损失对该概率的梯度；它们都用 query×key 两个轴索引。
 [E##\Delta_i=\sum_d O_{id}\,dO_{id}=\sum_j P_{ij}\,dP_{ij}]
 • [T#B#恒等式来源]：由 O_id=Σ_j P_ij V_jd 和 dP_ij=Σ_d dO_id V_jd，交换有限求和顺序，就得到两个表达式相等。
